--- a/app/udp_tool/output_excel_reports/ldm/03_Lubes_Sales_Marketing_Indirect_Channel_Portfolio_LDM_updated_UDP_Migration_Report.xlsx
+++ b/app/udp_tool/output_excel_reports/ldm/03_Lubes_Sales_Marketing_Indirect_Channel_Portfolio_LDM_updated_UDP_Migration_Report.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="UDP Definition" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="Value Reconciliation" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="Exceptions" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UDP Definition" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Value Reconciliation" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exceptions" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'UDP Definition'!$A$1:$N$1</definedName>
@@ -537,7 +537,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>2026-09-04 19:46:54</t>
+          <t>2026-09-05 21:16:23</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr"/>
@@ -563,7 +563,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>C:\Users\Shivansh\Downloads\migration-platform_4_sept_final\sappdmodels\ldm\03_Lubes_Sales_Marketing_Indirect_Channel_Portfolio_LDM_updated.ldm</t>
+          <t>C:\Users\SrinivasaPesala\Desktop\migration-platform_4_sept_final_h_l_m\sappdmodels\ldm\03_Lubes_Sales_Marketing_Indirect_Channel_Portfolio_LDM_updated.ldm</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">

--- a/app/udp_tool/output_excel_reports/ldm/03_Lubes_Sales_Marketing_Indirect_Channel_Portfolio_LDM_updated_UDP_Migration_Report.xlsx
+++ b/app/udp_tool/output_excel_reports/ldm/03_Lubes_Sales_Marketing_Indirect_Channel_Portfolio_LDM_updated_UDP_Migration_Report.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Summary" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="UDP Definition" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Value Reconciliation" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Exceptions" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="Summary" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="UDP Definition" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="Value Reconciliation" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="Exceptions" sheetId="4" state="visible" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">'UDP Definition'!$A$1:$N$1</definedName>
@@ -537,7 +537,7 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>2026-09-05 21:16:23</t>
+          <t>2026-09-05 20:21:02</t>
         </is>
       </c>
       <c r="C4" s="6" t="inlineStr"/>
@@ -563,7 +563,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>C:\Users\SrinivasaPesala\Desktop\migration-platform_4_sept_final_h_l_m\sappdmodels\ldm\03_Lubes_Sales_Marketing_Indirect_Channel_Portfolio_LDM_updated.ldm</t>
+          <t>C:\Users\Shivansh\Downloads\migration-platform_4_sept_final\sappdmodels\ldm\03_Lubes_Sales_Marketing_Indirect_Channel_Portfolio_LDM_updated.ldm</t>
         </is>
       </c>
       <c r="C6" s="6" t="inlineStr">
